--- a/artfynd/A 20803-2026 artfynd.xlsx
+++ b/artfynd/A 20803-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>118308405</v>
       </c>
       <c r="B2" t="n">
-        <v>90511</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,12 +775,7 @@
         <v>118308402</v>
       </c>
       <c r="B3" t="n">
-        <v>79573</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -879,37 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118308408</v>
+        <v>118308404</v>
       </c>
       <c r="B4" t="n">
-        <v>79572</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>521295</v>
+        <v>521435</v>
       </c>
       <c r="R4" t="n">
-        <v>6990715</v>
+        <v>6990660</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,37 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118308403</v>
+        <v>118308396</v>
       </c>
       <c r="B5" t="n">
-        <v>79601</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>521338</v>
+        <v>521178</v>
       </c>
       <c r="R5" t="n">
-        <v>6990812</v>
+        <v>6990664</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,37 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118308404</v>
+        <v>118308408</v>
       </c>
       <c r="B6" t="n">
-        <v>90476</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>521435</v>
+        <v>521295</v>
       </c>
       <c r="R6" t="n">
-        <v>6990660</v>
+        <v>6990715</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1182,6 +1157,103 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>118308403</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Boggsjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>521338</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6990812</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Sundsjö</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-07-02</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20803-2026 artfynd.xlsx
+++ b/artfynd/A 20803-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118308405</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118308402</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118308404</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118308396</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118308408</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,8 +1284,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118308403</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>